--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.03953182028486421</v>
       </c>
       <c r="C2" t="n">
-        <v>43489404</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>43489404</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>30676386</v>
+        <v>3957576</v>
       </c>
       <c r="L2" t="n">
-        <v>17928949</v>
+        <v>2063647</v>
       </c>
       <c r="M2" t="n">
-        <v>4591534</v>
+        <v>479457</v>
       </c>
       <c r="N2" t="n">
-        <v>259369</v>
+        <v>20737</v>
       </c>
       <c r="O2" t="n">
-        <v>2755084</v>
+        <v>303524</v>
       </c>
       <c r="P2" t="n">
-        <v>1116100</v>
+        <v>130709</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999473690986633</v>
+        <v>0.9998834729194641</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8934873938560486</v>
+        <v>0.8068235516548157</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7843366861343384</v>
+        <v>0.6315381526947021</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7156736850738525</v>
+        <v>0.5244919657707214</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5438075065612793</v>
+        <v>0.3063162863254547</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7721515893936157</v>
+        <v>0.595642626285553</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8277469277381897</v>
+        <v>0.6782608032226562</v>
       </c>
       <c r="X2" t="n">
-        <v>43489404</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>43489404</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>29820171</v>
+        <v>3879625</v>
       </c>
       <c r="AG2" t="n">
-        <v>16515869</v>
+        <v>1931326</v>
       </c>
       <c r="AH2" t="n">
-        <v>4154683</v>
+        <v>444442</v>
       </c>
       <c r="AI2" t="n">
-        <v>239231</v>
+        <v>19781</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2526940</v>
+        <v>281899</v>
       </c>
       <c r="AK2" t="n">
-        <v>1050221</v>
+        <v>123153</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8627481460571289</v>
+        <v>0.7857089638710022</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.736375093460083</v>
+        <v>0.6027695536613464</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6408821940422058</v>
+        <v>0.479902982711792</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3867009580135345</v>
+        <v>0.2238226681947708</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7105374932289124</v>
+        <v>0.5548602938652039</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7763077616691589</v>
+        <v>0.6372300982475281</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01104677445384101</v>
       </c>
       <c r="C3" t="n">
-        <v>564</v>
+        <v>209</v>
       </c>
       <c r="D3" t="n">
-        <v>30676386</v>
+        <v>3957576</v>
       </c>
       <c r="E3" t="n">
-        <v>3483330</v>
+        <v>859909</v>
       </c>
       <c r="F3" t="n">
-        <v>137927</v>
+        <v>43661</v>
       </c>
       <c r="G3" t="n">
-        <v>22764</v>
+        <v>5592</v>
       </c>
       <c r="H3" t="n">
-        <v>7031</v>
+        <v>3269</v>
       </c>
       <c r="I3" t="n">
-        <v>837</v>
+        <v>376</v>
       </c>
       <c r="J3" t="n">
-        <v>69001107</v>
+        <v>9856904</v>
       </c>
       <c r="K3" t="n">
-        <v>74507031</v>
+        <v>10252252</v>
       </c>
       <c r="L3" t="n">
-        <v>84941316</v>
+        <v>11606628</v>
       </c>
       <c r="M3" t="n">
-        <v>104154876</v>
+        <v>14701113</v>
       </c>
       <c r="N3" t="n">
-        <v>111654328</v>
+        <v>15934473</v>
       </c>
       <c r="O3" t="n">
-        <v>108115159</v>
+        <v>15354162</v>
       </c>
       <c r="P3" t="n">
-        <v>110907009</v>
+        <v>15814890</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8936039209365845</v>
+        <v>0.8125451803207397</v>
       </c>
       <c r="S3" t="n">
-        <v>0.792555570602417</v>
+        <v>0.6330658197402954</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7048957943916321</v>
+        <v>0.5130032896995544</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4177367687225342</v>
+        <v>0.2330890446901321</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7728874087333679</v>
+        <v>0.5949258208274841</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8245834112167358</v>
+        <v>0.6754742860794067</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>29820171</v>
+        <v>3879625</v>
       </c>
       <c r="Z3" t="n">
-        <v>4179710</v>
+        <v>907451</v>
       </c>
       <c r="AA3" t="n">
-        <v>223857</v>
+        <v>61002</v>
       </c>
       <c r="AB3" t="n">
-        <v>92525</v>
+        <v>17272</v>
       </c>
       <c r="AC3" t="n">
-        <v>11121</v>
+        <v>4608</v>
       </c>
       <c r="AD3" t="n">
-        <v>1455</v>
+        <v>634</v>
       </c>
       <c r="AE3" t="n">
-        <v>69003396</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>73419966</v>
+        <v>10141695</v>
       </c>
       <c r="AG3" t="n">
-        <v>83958367</v>
+        <v>11537872</v>
       </c>
       <c r="AH3" t="n">
-        <v>103650950</v>
+        <v>14654126</v>
       </c>
       <c r="AI3" t="n">
-        <v>111492494</v>
+        <v>15912837</v>
       </c>
       <c r="AJ3" t="n">
-        <v>107898698</v>
+        <v>15334057</v>
       </c>
       <c r="AK3" t="n">
-        <v>110836648</v>
+        <v>15806783</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8686623573303223</v>
+        <v>0.7965407371520996</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7300899028778076</v>
+        <v>0.5924736261367798</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6378300786018372</v>
+        <v>0.4755384027957916</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.385302722454071</v>
+        <v>0.2223433703184128</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.7088859081268311</v>
+        <v>0.5525394678115845</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7759114503860474</v>
+        <v>0.636426568031311</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.08512052685658661</v>
       </c>
       <c r="C4" t="n">
-        <v>227</v>
+        <v>87</v>
       </c>
       <c r="D4" t="n">
-        <v>3452179</v>
+        <v>887758</v>
       </c>
       <c r="E4" t="n">
-        <v>17928949</v>
+        <v>2063647</v>
       </c>
       <c r="F4" t="n">
-        <v>1080589</v>
+        <v>254757</v>
       </c>
       <c r="G4" t="n">
-        <v>38907</v>
+        <v>10445</v>
       </c>
       <c r="H4" t="n">
-        <v>108691</v>
+        <v>38090</v>
       </c>
       <c r="I4" t="n">
-        <v>12151</v>
+        <v>4983</v>
       </c>
       <c r="J4" t="n">
-        <v>2289</v>
+        <v>724</v>
       </c>
       <c r="K4" t="n">
-        <v>3656930</v>
+        <v>947556</v>
       </c>
       <c r="L4" t="n">
-        <v>4929791</v>
+        <v>1204005</v>
       </c>
       <c r="M4" t="n">
-        <v>1824147</v>
+        <v>434679</v>
       </c>
       <c r="N4" t="n">
-        <v>217581</v>
+        <v>46961</v>
       </c>
       <c r="O4" t="n">
-        <v>812977</v>
+        <v>206050</v>
       </c>
       <c r="P4" t="n">
-        <v>232259</v>
+        <v>62003</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999737143516541</v>
+        <v>0.9999417662620544</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8935456871986389</v>
+        <v>0.8096742033958435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7884247303009033</v>
+        <v>0.6323010921478271</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7102438807487488</v>
+        <v>0.5186840295791626</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4725074172019958</v>
+        <v>0.2647321820259094</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7725193500518799</v>
+        <v>0.5952839851379395</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8261620998382568</v>
+        <v>0.6768646836280823</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>4459579</v>
+        <v>981669</v>
       </c>
       <c r="Z4" t="n">
-        <v>16515869</v>
+        <v>1931326</v>
       </c>
       <c r="AA4" t="n">
-        <v>1381998</v>
+        <v>275114</v>
       </c>
       <c r="AB4" t="n">
-        <v>90806</v>
+        <v>18418</v>
       </c>
       <c r="AC4" t="n">
-        <v>154265</v>
+        <v>46413</v>
       </c>
       <c r="AD4" t="n">
-        <v>19176</v>
+        <v>6827</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>4743995</v>
+        <v>1058113</v>
       </c>
       <c r="AG4" t="n">
-        <v>5912740</v>
+        <v>1272761</v>
       </c>
       <c r="AH4" t="n">
-        <v>2328073</v>
+        <v>481666</v>
       </c>
       <c r="AI4" t="n">
-        <v>379415</v>
+        <v>68597</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1029438</v>
+        <v>226155</v>
       </c>
       <c r="AK4" t="n">
-        <v>302620</v>
+        <v>70110</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8656951785087585</v>
+        <v>0.791087806224823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7332190275192261</v>
+        <v>0.5975772738456726</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6393525004386902</v>
+        <v>0.4777107238769531</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3860006034374237</v>
+        <v>0.2230805605649948</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.7097107768058777</v>
+        <v>0.5536974668502808</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7761095762252808</v>
+        <v>0.6368280649185181</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>139</v>
       </c>
       <c r="D5" t="n">
-        <v>133790</v>
+        <v>42566</v>
       </c>
       <c r="E5" t="n">
-        <v>1228930</v>
+        <v>277850</v>
       </c>
       <c r="F5" t="n">
-        <v>4591534</v>
+        <v>479457</v>
       </c>
       <c r="G5" t="n">
-        <v>85102</v>
+        <v>16980</v>
       </c>
       <c r="H5" t="n">
-        <v>431547</v>
+        <v>103190</v>
       </c>
       <c r="I5" t="n">
-        <v>42454</v>
+        <v>14426</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3652453</v>
+        <v>913016</v>
       </c>
       <c r="L5" t="n">
-        <v>4692744</v>
+        <v>1196120</v>
       </c>
       <c r="M5" t="n">
-        <v>1922243</v>
+        <v>455151</v>
       </c>
       <c r="N5" t="n">
-        <v>361522</v>
+        <v>68229</v>
       </c>
       <c r="O5" t="n">
-        <v>809580</v>
+        <v>206664</v>
       </c>
       <c r="P5" t="n">
-        <v>237432</v>
+        <v>62798</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999796748161316</v>
+        <v>0.9999549388885498</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9350235462188721</v>
+        <v>0.8842236399650574</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9144608974456787</v>
+        <v>0.850649356842041</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9666966199874878</v>
+        <v>0.9446292519569397</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9948520660400391</v>
+        <v>0.9928321838378906</v>
       </c>
       <c r="V5" t="n">
-        <v>0.985576331615448</v>
+        <v>0.9743183851242065</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9958246946334839</v>
+        <v>0.9922341108322144</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>191095</v>
+        <v>55693</v>
       </c>
       <c r="Z5" t="n">
-        <v>1457880</v>
+        <v>288452</v>
       </c>
       <c r="AA5" t="n">
-        <v>4154683</v>
+        <v>444442</v>
       </c>
       <c r="AB5" t="n">
-        <v>109952</v>
+        <v>18491</v>
       </c>
       <c r="AC5" t="n">
-        <v>540534</v>
+        <v>110393</v>
       </c>
       <c r="AD5" t="n">
-        <v>59633</v>
+        <v>17137</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>4508668</v>
+        <v>990967</v>
       </c>
       <c r="AG5" t="n">
-        <v>6105824</v>
+        <v>1328441</v>
       </c>
       <c r="AH5" t="n">
-        <v>2359094</v>
+        <v>490166</v>
       </c>
       <c r="AI5" t="n">
-        <v>381660</v>
+        <v>69185</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1037724</v>
+        <v>228289</v>
       </c>
       <c r="AK5" t="n">
-        <v>303311</v>
+        <v>70354</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9177488684654236</v>
+        <v>0.8724935054779053</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8931614756584167</v>
+        <v>0.8381370902061462</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9583336114883423</v>
+        <v>0.9395265579223633</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9932344555854797</v>
+        <v>0.9914263486862183</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9816240668296814</v>
+        <v>0.9717216491699219</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9946135878562927</v>
+        <v>0.9912594556808472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>756</v>
+        <v>202</v>
       </c>
       <c r="D6" t="n">
-        <v>66168</v>
+        <v>14300</v>
       </c>
       <c r="E6" t="n">
-        <v>94457</v>
+        <v>20160</v>
       </c>
       <c r="F6" t="n">
-        <v>126084</v>
+        <v>18681</v>
       </c>
       <c r="G6" t="n">
-        <v>259369</v>
+        <v>20737</v>
       </c>
       <c r="H6" t="n">
-        <v>64955</v>
+        <v>12498</v>
       </c>
       <c r="I6" t="n">
-        <v>9102</v>
+        <v>2388</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>83128</v>
+        <v>15475</v>
       </c>
       <c r="Z6" t="n">
-        <v>95644</v>
+        <v>19911</v>
       </c>
       <c r="AA6" t="n">
-        <v>116433</v>
+        <v>18620</v>
       </c>
       <c r="AB6" t="n">
-        <v>239231</v>
+        <v>19781</v>
       </c>
       <c r="AC6" t="n">
-        <v>75066</v>
+        <v>12539</v>
       </c>
       <c r="AD6" t="n">
-        <v>11389</v>
+        <v>2640</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>4505</v>
+        <v>2849</v>
       </c>
       <c r="E7" t="n">
-        <v>115109</v>
+        <v>42462</v>
       </c>
       <c r="F7" t="n">
-        <v>456980</v>
+        <v>109327</v>
       </c>
       <c r="G7" t="n">
-        <v>65093</v>
+        <v>12135</v>
       </c>
       <c r="H7" t="n">
-        <v>2755084</v>
+        <v>303524</v>
       </c>
       <c r="I7" t="n">
-        <v>167715</v>
+        <v>39830</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>9749</v>
+        <v>5163</v>
       </c>
       <c r="Z7" t="n">
-        <v>166537</v>
+        <v>51800</v>
       </c>
       <c r="AA7" t="n">
-        <v>572579</v>
+        <v>116271</v>
       </c>
       <c r="AB7" t="n">
-        <v>77892</v>
+        <v>12183</v>
       </c>
       <c r="AC7" t="n">
-        <v>2526940</v>
+        <v>281899</v>
       </c>
       <c r="AD7" t="n">
-        <v>210967</v>
+        <v>42872</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="E8" t="n">
-        <v>7965</v>
+        <v>3624</v>
       </c>
       <c r="F8" t="n">
-        <v>22567</v>
+        <v>8253</v>
       </c>
       <c r="G8" t="n">
-        <v>5715</v>
+        <v>1809</v>
       </c>
       <c r="H8" t="n">
-        <v>200753</v>
+        <v>49003</v>
       </c>
       <c r="I8" t="n">
-        <v>1116100</v>
+        <v>130709</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>444</v>
+        <v>113</v>
       </c>
       <c r="Z8" t="n">
-        <v>12969</v>
+        <v>5147</v>
       </c>
       <c r="AA8" t="n">
-        <v>33206</v>
+        <v>10659</v>
       </c>
       <c r="AB8" t="n">
-        <v>8240</v>
+        <v>2233</v>
       </c>
       <c r="AC8" t="n">
-        <v>248452</v>
+        <v>52202</v>
       </c>
       <c r="AD8" t="n">
-        <v>1050221</v>
+        <v>123153</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
